--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20261020.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20261020.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>53,028,505</t>
+          <t>122,805</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>122,805</t>
+          <t>53,028,505</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
